--- a/master/result/12_霸道总裁：独家宠爱/12_霸道总裁.xlsx
+++ b/master/result/12_霸道总裁：独家宠爱/12_霸道总裁.xlsx
@@ -397,544 +397,689 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:D48"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>superior</v>
       </c>
       <c r="B2" t="str">
-        <v>superior</v>
+        <v>/superior/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>上级</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>succeed</v>
       </c>
       <c r="B3" t="str">
-        <v>succeed</v>
+        <v>/succeed/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>成功</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>fashionable</v>
       </c>
       <c r="B4" t="str">
-        <v>fashionable</v>
+        <v>/fashionable/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>时髦</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>enemy</v>
       </c>
       <c r="B5" t="str">
-        <v>enemy</v>
+        <v>/enemy/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>敌人</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>similar</v>
       </c>
       <c r="B6" t="str">
-        <v>similar</v>
+        <v>/similar/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>相似</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>indicate</v>
       </c>
       <c r="B7" t="str">
-        <v>indicate</v>
+        <v>/ˈɪndɪkeɪt/</v>
       </c>
       <c r="C7" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D7" t="str">
         <v>暗示</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>adjacent</v>
       </c>
       <c r="B8" t="str">
-        <v>adjacent</v>
+        <v>/adjacent/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>相邻</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>suppose</v>
       </c>
       <c r="B9" t="str">
-        <v>suppose</v>
+        <v>/səˈpəʊz/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>猜想</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>wholly</v>
       </c>
       <c r="B10" t="str">
-        <v>wholly</v>
+        <v>/wholly/</v>
       </c>
       <c r="C10" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>完全</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>irony</v>
       </c>
       <c r="B11" t="str">
-        <v>irony</v>
+        <v>/irony/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>讽刺</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>gamble</v>
       </c>
       <c r="B12" t="str">
-        <v>gamble</v>
+        <v>/gamble/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>赌博</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>ambition</v>
       </c>
       <c r="B13" t="str">
-        <v>ambition</v>
+        <v>/æmˈbɪʃn/</v>
       </c>
       <c r="C13" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>野心</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>method</v>
       </c>
       <c r="B14" t="str">
-        <v>method</v>
+        <v>/method/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>方法</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>countryside</v>
       </c>
       <c r="B15" t="str">
-        <v>countryside</v>
+        <v>/ˈkʌntrisaɪd/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>乡下</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>import</v>
       </c>
       <c r="B16" t="str">
-        <v>import</v>
+        <v>/ɪmˈpɔːt/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>进口</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>question</v>
       </c>
       <c r="B17" t="str">
-        <v>question</v>
+        <v>/ˈkwestʃən/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>问题</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>meeting</v>
       </c>
       <c r="B18" t="str">
-        <v>meeting</v>
+        <v>/meeting/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>会议</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>turbulent</v>
       </c>
       <c r="B19" t="str">
-        <v>turbulent</v>
+        <v>/turbulent/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>动荡</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>random</v>
       </c>
       <c r="B20" t="str">
-        <v>random</v>
+        <v>/random/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>随机</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>tall</v>
       </c>
       <c r="B21" t="str">
-        <v>tall</v>
+        <v>/tall/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>高大</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>confuse</v>
       </c>
       <c r="B22" t="str">
-        <v>confuse</v>
+        <v>/confuse/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>困惑</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>why</v>
       </c>
       <c r="B23" t="str">
-        <v>why</v>
+        <v>/why/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>为什么</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>balance</v>
       </c>
       <c r="B24" t="str">
-        <v>balance</v>
+        <v>/ˈbæləns/</v>
       </c>
       <c r="C24" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>平衡</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>simple</v>
       </c>
       <c r="B25" t="str">
-        <v>simple</v>
+        <v>/simple/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>简单</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>decade</v>
       </c>
       <c r="B26" t="str">
-        <v>decade</v>
+        <v>/decade/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>十年</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>phase</v>
       </c>
       <c r="B27" t="str">
-        <v>phase</v>
+        <v>/phase/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>阶段</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>jealous</v>
       </c>
       <c r="B28" t="str">
-        <v>jealous</v>
+        <v>/jealous/</v>
       </c>
       <c r="C28" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>嫉妒</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>interfere</v>
       </c>
       <c r="B29" t="str">
-        <v>interfere</v>
+        <v>/ˌɪntəˈfɪə/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>干涉</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>thirst</v>
       </c>
       <c r="B30" t="str">
-        <v>thirst</v>
+        <v>/thirst/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>渴望</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>jungle</v>
       </c>
       <c r="B31" t="str">
-        <v>jungle</v>
+        <v>/jungle/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>丛林</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>offer</v>
       </c>
       <c r="B32" t="str">
-        <v>offer</v>
+        <v>/ˈɒfə/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>提议</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>partner</v>
       </c>
       <c r="B33" t="str">
-        <v>partner</v>
+        <v>/partner/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>伙伴</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>nod</v>
       </c>
       <c r="B34" t="str">
-        <v>nod</v>
+        <v>/nɒd/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>点头</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>torture</v>
       </c>
       <c r="B35" t="str">
-        <v>torture</v>
+        <v>/torture/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>折磨</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>inferior</v>
       </c>
       <c r="B36" t="str">
-        <v>inferior</v>
+        <v>/inferior/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>低等</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>multiple</v>
       </c>
       <c r="B37" t="str">
-        <v>multiple</v>
+        <v>/multiple/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>多重</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>snowstorm</v>
       </c>
       <c r="B38" t="str">
-        <v>snowstorm</v>
+        <v>/snowstorm/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>暴风雪</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>eighty</v>
       </c>
       <c r="B39" t="str">
-        <v>eighty</v>
+        <v>/eighty/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>八十</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>couple</v>
       </c>
       <c r="B40" t="str">
-        <v>couple</v>
+        <v>/couple/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>情侣</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>leader</v>
       </c>
       <c r="B41" t="str">
-        <v>leader</v>
+        <v>/leader/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>领导者</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>passion</v>
       </c>
       <c r="B42" t="str">
-        <v>passion</v>
+        <v>/passion/</v>
       </c>
       <c r="C42" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>激情</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>competitor</v>
       </c>
       <c r="B43" t="str">
-        <v>competitor</v>
+        <v>/kəmˈpetɪtə/</v>
       </c>
       <c r="C43" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>竞争对手</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>surprise</v>
       </c>
       <c r="B44" t="str">
-        <v>surprise</v>
+        <v>/səˈpraɪz/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>惊喜</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>protect</v>
       </c>
       <c r="B45" t="str">
-        <v>protect</v>
+        <v>/prəˈtekt/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>保护</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>birth</v>
       </c>
       <c r="B46" t="str">
-        <v>birth</v>
+        <v>/birth/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>出生</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>award</v>
       </c>
       <c r="B47" t="str">
-        <v>award</v>
+        <v>/award/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>奖励</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>bottom</v>
       </c>
       <c r="B48" t="str">
-        <v>bottom</v>
+        <v>/bottom/</v>
       </c>
       <c r="C48" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D48" t="str">
         <v>底部</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D48"/>
   </ignoredErrors>
 </worksheet>
 </file>